--- a/biblioteca/materiais/Raio-X-Financeiro-FQC.xlsx
+++ b/biblioteca/materiais/Raio-X-Financeiro-FQC.xlsx
@@ -325,7 +325,7 @@
     <t xml:space="preserve">Índice de endividamento</t>
   </si>
   <si>
-    <t xml:space="preserve">Parcelas de dívidas ÷ entradas. Ideal: até 30%.</t>
+    <t xml:space="preserve">Parcelas de dívidas ÷ entradas. Saudável: até 10%. Atenção: até 20%. Acima disso, renegociar vira prioridade.</t>
   </si>
   <si>
     <t xml:space="preserve">Meses de reserva</t>
@@ -1844,7 +1844,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="26" t="s">
         <v>92</v>
       </c>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D17" s="32" t="str">
         <f aca="false">IF(C17&lt;=$C$28,"Saudável",IF(C17&lt;=$C$29,"Atenção","Alerta"))</f>
-        <v>Saudável</v>
+        <v>Atenção</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>93</v>
@@ -1946,7 +1946,7 @@
         <v>104</v>
       </c>
       <c r="C28" s="38" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1954,7 +1954,7 @@
         <v>105</v>
       </c>
       <c r="C29" s="38" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
